--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260917.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>69,370,958</t>
+          <t>26,220,018</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>26,220,018</t>
+          <t>69,370,958</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>26,245,459</t>
+          <t>247,475,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>247,475,386</t>
+          <t>26,245,459</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
